--- a/Data_Analysis/Sensitivity analysis/Hybrid/sweep_results_hybrid_G3_task017.xlsx
+++ b/Data_Analysis/Sensitivity analysis/Hybrid/sweep_results_hybrid_G3_task017.xlsx
@@ -100,13 +100,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.85546875" customWidth="true"/>
     <col min="2" max="2" width="14.85546875" customWidth="true"/>
     <col min="3" max="3" width="13.28515625" customWidth="true"/>
-    <col min="4" max="4" width="10" customWidth="true"/>
+    <col min="4" max="4" width="11.7109375" customWidth="true"/>
     <col min="5" max="5" width="9.5703125" customWidth="true"/>
     <col min="6" max="6" width="16.140625" customWidth="true"/>
     <col min="7" max="7" width="20.85546875" customWidth="true"/>
@@ -207,6 +207,94 @@
         <v>5.6652867693479392</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="0">
+        <v>224</v>
+      </c>
+      <c r="B3" s="0">
+        <v>50</v>
+      </c>
+      <c r="C3" s="0">
+        <v>224</v>
+      </c>
+      <c r="D3" s="0">
+        <v>94.095737804017517</v>
+      </c>
+      <c r="E3" s="0">
+        <v>456.44</v>
+      </c>
+      <c r="F3" s="0">
+        <v>161.36095034076081</v>
+      </c>
+      <c r="G3" s="0">
+        <v>4127.2097322298678</v>
+      </c>
+      <c r="H3" s="0">
+        <v>-1286.0689296548139</v>
+      </c>
+      <c r="I3" s="0">
+        <v>4.9800000000000004</v>
+      </c>
+      <c r="J3" s="0">
+        <v>12.105</v>
+      </c>
+      <c r="K3" s="0">
+        <v>2.2399999999999998</v>
+      </c>
+      <c r="L3" s="0">
+        <v>3.2499999999999996</v>
+      </c>
+      <c r="M3" s="0">
+        <v>300.08393367783447</v>
+      </c>
+      <c r="N3" s="0">
+        <v>5.6652867693479392</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0">
+        <v>224</v>
+      </c>
+      <c r="B4" s="0">
+        <v>51</v>
+      </c>
+      <c r="C4" s="0">
+        <v>224</v>
+      </c>
+      <c r="D4" s="0">
+        <v>94.051098923014436</v>
+      </c>
+      <c r="E4" s="0">
+        <v>462.54000000000002</v>
+      </c>
+      <c r="F4" s="0">
+        <v>159.23291428533071</v>
+      </c>
+      <c r="G4" s="0">
+        <v>4232.5103820921731</v>
+      </c>
+      <c r="H4" s="0">
+        <v>-1250.5808707372191</v>
+      </c>
+      <c r="I4" s="0">
+        <v>5.1900000000000004</v>
+      </c>
+      <c r="J4" s="0">
+        <v>12.615</v>
+      </c>
+      <c r="K4" s="0">
+        <v>2.4049999999999994</v>
+      </c>
+      <c r="L4" s="0">
+        <v>3.4899999999999998</v>
+      </c>
+      <c r="M4" s="0">
+        <v>300.08394505954635</v>
+      </c>
+      <c r="N4" s="0">
+        <v>5.6652867693479392</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>